--- a/diurenmw/Excels/WeaponObj_武器类型表.xlsx
+++ b/diurenmw/Excels/WeaponObj_武器类型表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -87,6 +87,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>武器种类：</t>
     </r>
     <r>
@@ -146,6 +152,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>品级：</t>
     </r>
     <r>
@@ -280,6 +292,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>技能伤增加</t>
     </r>
     <r>
@@ -303,6 +321,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>攻击力增加</t>
     </r>
     <r>
@@ -326,6 +350,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>防御力增加</t>
     </r>
     <r>
@@ -349,6 +379,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>血量增加</t>
     </r>
     <r>
@@ -1607,7 +1643,7 @@
         <v>3</v>
       </c>
       <c r="N5">
-        <v>37668</v>
+        <v>150552</v>
       </c>
       <c r="O5">
         <v>1</v>
@@ -1654,7 +1690,7 @@
         <v>43</v>
       </c>
       <c r="N6">
-        <v>37668</v>
+        <v>150562</v>
       </c>
       <c r="O6">
         <v>1</v>
@@ -1717,6 +1753,9 @@
       <c r="I11" s="1">
         <v>6</v>
       </c>
+      <c r="N11">
+        <v>103433</v>
+      </c>
       <c r="O11">
         <v>1</v>
       </c>
@@ -1757,6 +1796,9 @@
       </c>
       <c r="M12" s="10" t="s">
         <v>49</v>
+      </c>
+      <c r="N12">
+        <v>140339</v>
       </c>
       <c r="O12">
         <v>1</v>
@@ -1801,6 +1843,9 @@
       <c r="I15" s="1">
         <v>5</v>
       </c>
+      <c r="N15">
+        <v>37668</v>
+      </c>
       <c r="O15">
         <v>1</v>
       </c>
@@ -1841,6 +1886,9 @@
       </c>
       <c r="M16" s="10" t="s">
         <v>59</v>
+      </c>
+      <c r="N16">
+        <v>37668</v>
       </c>
       <c r="O16">
         <v>1</v>

--- a/diurenmw/Excels/WeaponObj_武器类型表.xlsx
+++ b/diurenmw/Excels/WeaponObj_武器类型表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1773,6 +1773,9 @@
       <c r="D12" s="6">
         <v>4</v>
       </c>
+      <c r="E12" s="2">
+        <v>179329</v>
+      </c>
       <c r="F12" s="4" t="s">
         <v>39</v>
       </c>
@@ -1798,7 +1801,7 @@
         <v>49</v>
       </c>
       <c r="N12">
-        <v>140339</v>
+        <v>194519</v>
       </c>
       <c r="O12">
         <v>1</v>
@@ -1831,6 +1834,9 @@
       <c r="D15" s="6">
         <v>1</v>
       </c>
+      <c r="E15" s="2">
+        <v>26755</v>
+      </c>
       <c r="F15" s="4" t="s">
         <v>51</v>
       </c>
@@ -1844,7 +1850,7 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>37668</v>
+        <v>26755</v>
       </c>
       <c r="O15">
         <v>1</v>
@@ -1863,6 +1869,9 @@
       <c r="D16" s="6">
         <v>4</v>
       </c>
+      <c r="E16" s="2">
+        <v>278406</v>
+      </c>
       <c r="F16" s="4" t="s">
         <v>54</v>
       </c>
@@ -1888,7 +1897,7 @@
         <v>59</v>
       </c>
       <c r="N16">
-        <v>37668</v>
+        <v>278406</v>
       </c>
       <c r="O16">
         <v>1</v>

--- a/diurenmw/Excels/WeaponObj_武器类型表.xlsx
+++ b/diurenmw/Excels/WeaponObj_武器类型表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="67">
   <si>
     <t>int</t>
   </si>
@@ -83,7 +83,15 @@
     <t>ID</t>
   </si>
   <si>
-    <t>名称</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>名称</t>
+    </r>
   </si>
   <si>
     <r>
@@ -234,40 +242,217 @@
     </r>
   </si>
   <si>
-    <t>模型</t>
-  </si>
-  <si>
-    <t>物理攻击力范围</t>
-  </si>
-  <si>
-    <t>魔法攻击力范围</t>
-  </si>
-  <si>
-    <t>力量</t>
-  </si>
-  <si>
-    <t>智力</t>
-  </si>
-  <si>
-    <t>效果1描述</t>
-  </si>
-  <si>
-    <t>效果2描述</t>
-  </si>
-  <si>
-    <t>效果3描述</t>
-  </si>
-  <si>
-    <t>效果4描述</t>
-  </si>
-  <si>
-    <t>图标资源id</t>
-  </si>
-  <si>
-    <t>堆叠数量上限</t>
-  </si>
-  <si>
-    <t>生锈的铁剑</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>模型</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>物理攻击力范围</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>魔法攻击力范围</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>力量</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>智力</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>效果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>描述</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>效果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>描述</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>效果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>描述</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>效果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>描述</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>图标资源</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>id</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>堆叠数量上限</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>生锈的铁剑</t>
+    </r>
   </si>
   <si>
     <t>ED1D823242771BAA249294A58DE4710A</t>
@@ -279,7 +464,15 @@
     <t>7|10</t>
   </si>
   <si>
-    <t>石中剑</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>石中剑</t>
+    </r>
   </si>
   <si>
     <t>4D82B7F549634FA3E420FA80E2FB3CD3</t>
@@ -407,25 +600,286 @@
     </r>
   </si>
   <si>
-    <t>树枝</t>
-  </si>
-  <si>
-    <t>陨星杖</t>
-  </si>
-  <si>
-    <t>技能伤增加20％</t>
-  </si>
-  <si>
-    <t>技能CD减少20％</t>
-  </si>
-  <si>
-    <t>释放技能时10％几率召唤陨石</t>
-  </si>
-  <si>
-    <t>释放技能时1％几率召唤大陨石</t>
-  </si>
-  <si>
-    <t>随时会断的弓</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>破空剑</t>
+    </r>
+  </si>
+  <si>
+    <t>415|470</t>
+  </si>
+  <si>
+    <t>209|237</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>暴击率增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>％</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>爆伤增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>％</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>剑气波数量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>拔刀斩技能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>CD-2s</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>树枝</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>陨星杖</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>技能伤增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>％</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>技能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>CD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>减少</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>％</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>释放技能时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>％几率召唤陨石</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>释放技能时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>％几率召唤大陨石</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>随时会断的弓</t>
+    </r>
   </si>
   <si>
     <t>14|18</t>
@@ -434,7 +888,15 @@
     <t>13|16</t>
   </si>
   <si>
-    <t>月神的弓弦</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月神的弓弦</t>
+    </r>
   </si>
   <si>
     <t>350|410</t>
@@ -443,16 +905,102 @@
     <t>330|395</t>
   </si>
   <si>
-    <t>攻击速度增加10％</t>
-  </si>
-  <si>
-    <t>攻击力增加20％</t>
-  </si>
-  <si>
-    <t>命中时使敌人减速10％</t>
-  </si>
-  <si>
-    <t>箭矢附带冰蓝色拖尾</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击速度增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>％</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击力增加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>％</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>命中时使敌人减速</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>％</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>箭矢附带冰蓝色拖尾</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -465,7 +1013,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -474,15 +1022,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
@@ -629,6 +1177,18 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -1078,32 +1638,29 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1455,7 +2012,7 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:O35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.575" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.0083333333333" style="2" customWidth="1"/>
@@ -1466,282 +2023,322 @@
     <col min="10" max="10" width="13" style="2" customWidth="1"/>
     <col min="11" max="11" width="14.625" style="2" customWidth="1"/>
     <col min="12" max="12" width="14.125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="13.875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="15.375" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1" spans="1:15">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="10" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" spans="1:15">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="10" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" ht="82.5" customHeight="1" spans="1:15">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" spans="1:2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="4"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
     </row>
     <row r="5" ht="18.75" customHeight="1" spans="1:15">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <v>1001</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="7">
         <v>1</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="7">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="7">
         <v>6</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="7">
         <v>3</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="3">
         <v>150552</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:15">
-      <c r="A6" s="6">
+      <c r="A6" s="7">
         <v>1002</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="7">
         <v>1</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="7">
         <v>4</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="7">
         <v>170</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="7">
         <v>90</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="M6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="3">
         <v>150562</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="7" ht="18.75" customHeight="1" spans="1:7">
-      <c r="A7" s="6"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
+    <row r="7" ht="18.75" customHeight="1" spans="1:15">
+      <c r="A7" s="7">
+        <v>1003</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2">
+        <v>31734</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="1">
+        <v>177</v>
+      </c>
+      <c r="I7" s="1">
+        <v>95</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N7" s="3">
+        <v>166600</v>
+      </c>
+      <c r="O7" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:7">
-      <c r="A8" s="6"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
     </row>
     <row r="9" ht="18.75" customHeight="1" spans="1:7">
-      <c r="A9" s="6"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:7">
-      <c r="A10" s="6"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:15">
-      <c r="A11" s="6">
+      <c r="A11" s="7">
         <v>2001</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="6">
+      <c r="B11" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="7">
         <v>2</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="7">
         <v>1</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G11" s="8" t="s">
@@ -1753,33 +2350,33 @@
       <c r="I11" s="1">
         <v>6</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="3">
         <v>103433</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="12" ht="27" spans="1:15">
-      <c r="A12" s="6">
+    <row r="12" ht="28.5" spans="1:15">
+      <c r="A12" s="7">
         <v>2002</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="6">
+      <c r="B12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="7">
         <v>2</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="7">
         <v>4</v>
       </c>
       <c r="E12" s="2">
         <v>179329</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="5" t="s">
         <v>38</v>
       </c>
       <c r="H12" s="1">
@@ -1788,60 +2385,60 @@
       <c r="I12" s="1">
         <v>170</v>
       </c>
-      <c r="J12" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="N12">
+      <c r="J12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" s="3">
         <v>194519</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1" spans="1:6">
-      <c r="A13" s="6"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="F13" s="4"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="F13" s="5"/>
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:6">
-      <c r="A14" s="6"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="F14" s="4"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="F14" s="5"/>
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:15">
-      <c r="A15" s="6">
+      <c r="A15" s="7">
         <v>3001</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="6">
+      <c r="B15" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="7">
         <v>3</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="7">
         <v>1</v>
       </c>
       <c r="E15" s="2">
         <v>26755</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>52</v>
+      <c r="F15" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="H15" s="1">
         <v>5</v>
@@ -1849,34 +2446,34 @@
       <c r="I15" s="1">
         <v>5</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="3">
         <v>26755</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="16" ht="27" spans="1:15">
-      <c r="A16" s="6">
+    <row r="16" ht="28.5" spans="1:15">
+      <c r="A16" s="7">
         <v>3002</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="6">
+      <c r="B16" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="7">
         <v>3</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="7">
         <v>4</v>
       </c>
       <c r="E16" s="2">
         <v>278406</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>55</v>
+      <c r="F16" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="H16" s="1">
         <v>130</v>
@@ -1884,66 +2481,66 @@
       <c r="I16" s="1">
         <v>130</v>
       </c>
-      <c r="J16" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="L16" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="M16" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="N16">
+      <c r="J16" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="N16" s="3">
         <v>278406</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:6">
-      <c r="A17" s="6"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="F17" s="4"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="F17" s="5"/>
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:6">
-      <c r="A18" s="6"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="F18" s="4"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="F18" s="5"/>
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:6">
-      <c r="A19" s="6"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="F19" s="4"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="F19" s="5"/>
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:6">
-      <c r="A20" s="6"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="F20" s="4"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="F20" s="5"/>
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:6">
-      <c r="A21" s="6"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="F21" s="4"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="F21" s="5"/>
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:6">
-      <c r="A22" s="6"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="F22" s="4"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="9"/>

--- a/diurenmw/Excels/WeaponObj_武器类型表.xlsx
+++ b/diurenmw/Excels/WeaponObj_武器类型表.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="242">
   <si>
     <t>int</t>
   </si>
@@ -445,7 +445,7 @@
     <t>千年玄铁剑</t>
   </si>
   <si>
-    <t/>
+    <t>攻击时有3%的概率增加10点力量和智力持续20秒</t>
   </si>
   <si>
     <t>精炼的巨剑</t>
@@ -454,6 +454,9 @@
     <t>梅丽莎的长剑</t>
   </si>
   <si>
+    <t>攻击时有3%的概率增加25点力量和智力持续20秒</t>
+  </si>
+  <si>
     <t>惊风剑</t>
   </si>
   <si>
@@ -520,7 +523,7 @@
     <t xml:space="preserve">伤害增加3% </t>
   </si>
   <si>
-    <t>攻击时，有5%概率使敌人进入中毒状态</t>
+    <t>攻击时，有3%概率使敌人进入中毒状态</t>
   </si>
   <si>
     <t>银河骑士长剑</t>
@@ -691,10 +694,10 @@
     <t>陨星杖</t>
   </si>
   <si>
+    <t>3E47D9AF43AFC2A32FC3A4B2A45D595E</t>
+  </si>
+  <si>
     <t>200|225</t>
-  </si>
-  <si>
-    <t>400|450</t>
   </si>
   <si>
     <t>技能伤增加20％</t>
@@ -786,7 +789,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -802,9 +805,6 @@
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -1117,26 +1117,26 @@
   <dimension ref="A1:T88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="17.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="15.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="15.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="43.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="8" width="60.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="8" width="35.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="8" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="8" width="25.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="7" width="13.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="17.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="15.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="15.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="43.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="7" width="60.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="7" width="46.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="7" width="25.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="6" width="13.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -1243,7 +1243,7 @@
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="69.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -3185,7 +3185,7 @@
       <c r="I46" s="5">
         <v>0</v>
       </c>
-      <c r="J46" s="6" t="s">
+      <c r="J46" s="2" t="s">
         <v>143</v>
       </c>
       <c r="K46" s="3"/>
@@ -3279,8 +3279,8 @@
       <c r="I48" s="5">
         <v>0</v>
       </c>
-      <c r="J48" s="6" t="s">
-        <v>143</v>
+      <c r="J48" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
@@ -3304,7 +3304,7 @@
         <v>1045</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C49" s="5">
         <v>1</v>
@@ -3350,7 +3350,7 @@
         <v>1046</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C50" s="5">
         <v>1</v>
@@ -3362,10 +3362,10 @@
         <v>103058</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H50" s="5">
         <v>20</v>
@@ -3396,7 +3396,7 @@
         <v>1047</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C51" s="5">
         <v>1</v>
@@ -3420,10 +3420,10 @@
         <v>0</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
@@ -3446,7 +3446,7 @@
         <v>1048</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C52" s="5">
         <v>1</v>
@@ -3492,7 +3492,7 @@
         <v>1049</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C53" s="5">
         <v>1</v>
@@ -3538,7 +3538,7 @@
         <v>1050</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C54" s="5">
         <v>1</v>
@@ -3550,10 +3550,10 @@
         <v>103058</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H54" s="5">
         <v>24</v>
@@ -3562,10 +3562,10 @@
         <v>0</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
@@ -3588,7 +3588,7 @@
         <v>1051</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C55" s="5">
         <v>1</v>
@@ -3600,10 +3600,10 @@
         <v>103058</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H55" s="5">
         <v>24</v>
@@ -3612,7 +3612,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
@@ -3636,7 +3636,7 @@
         <v>1052</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C56" s="5">
         <v>1</v>
@@ -3648,7 +3648,7 @@
         <v>103058</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>116</v>
@@ -3682,7 +3682,7 @@
         <v>1053</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C57" s="5">
         <v>1</v>
@@ -3694,10 +3694,10 @@
         <v>103058</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H57" s="5">
         <v>27</v>
@@ -3706,10 +3706,10 @@
         <v>0</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
@@ -3732,7 +3732,7 @@
         <v>1054</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C58" s="5">
         <v>1</v>
@@ -3744,10 +3744,10 @@
         <v>103058</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H58" s="5">
         <v>27</v>
@@ -3778,7 +3778,7 @@
         <v>1055</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C59" s="5">
         <v>1</v>
@@ -3790,10 +3790,10 @@
         <v>103058</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H59" s="5">
         <v>27</v>
@@ -3802,7 +3802,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="3"/>
@@ -3826,7 +3826,7 @@
         <v>1056</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C60" s="5">
         <v>1</v>
@@ -3838,10 +3838,10 @@
         <v>103058</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H60" s="5">
         <v>29</v>
@@ -3850,10 +3850,10 @@
         <v>0</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
@@ -3876,7 +3876,7 @@
         <v>1057</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C61" s="5">
         <v>1</v>
@@ -3888,10 +3888,10 @@
         <v>103058</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H61" s="5">
         <v>30</v>
@@ -3900,10 +3900,10 @@
         <v>0</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
@@ -3926,7 +3926,7 @@
         <v>1058</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C62" s="5">
         <v>1</v>
@@ -3938,10 +3938,10 @@
         <v>103058</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H62" s="5">
         <v>30</v>
@@ -3950,10 +3950,10 @@
         <v>0</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
@@ -3976,7 +3976,7 @@
         <v>1059</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C63" s="5">
         <v>1</v>
@@ -3988,10 +3988,10 @@
         <v>103058</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H63" s="5">
         <v>30</v>
@@ -4022,7 +4022,7 @@
         <v>1060</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C64" s="5">
         <v>1</v>
@@ -4034,10 +4034,10 @@
         <v>103058</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H64" s="5">
         <v>38</v>
@@ -4046,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K64" s="3"/>
       <c r="L64" s="3"/>
@@ -4070,7 +4070,7 @@
         <v>1061</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C65" s="5">
         <v>1</v>
@@ -4082,10 +4082,10 @@
         <v>103058</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H65" s="5">
         <v>38</v>
@@ -4116,7 +4116,7 @@
         <v>1062</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C66" s="5">
         <v>1</v>
@@ -4128,10 +4128,10 @@
         <v>103058</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H66" s="5">
         <v>38</v>
@@ -4140,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K66" s="3"/>
       <c r="L66" s="3"/>
@@ -4186,7 +4186,7 @@
         <v>1063</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C68" s="5">
         <v>1</v>
@@ -4195,13 +4195,13 @@
         <v>4</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H68" s="5">
         <v>39</v>
@@ -4210,10 +4210,10 @@
         <v>0</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
@@ -4236,7 +4236,7 @@
         <v>1064</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C69" s="5">
         <v>1</v>
@@ -4245,13 +4245,13 @@
         <v>4</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H69" s="5">
         <v>39</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
@@ -4286,7 +4286,7 @@
         <v>1065</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C70" s="5">
         <v>1</v>
@@ -4295,13 +4295,13 @@
         <v>4</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H70" s="5">
         <v>39</v>
@@ -4310,10 +4310,10 @@
         <v>0</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
@@ -4336,7 +4336,7 @@
         <v>1066</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C71" s="5">
         <v>1</v>
@@ -4345,13 +4345,13 @@
         <v>4</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H71" s="5">
         <v>39</v>
@@ -4360,10 +4360,10 @@
         <v>0</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
@@ -4386,7 +4386,7 @@
         <v>1067</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C72" s="5">
         <v>1</v>
@@ -4395,13 +4395,13 @@
         <v>4</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H72" s="5">
         <v>39</v>
@@ -4410,10 +4410,10 @@
         <v>0</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L72" s="3"/>
       <c r="M72" s="3"/>
@@ -4436,7 +4436,7 @@
         <v>1068</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C73" s="5">
         <v>1</v>
@@ -4445,13 +4445,13 @@
         <v>4</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H73" s="5">
         <v>39</v>
@@ -4460,10 +4460,10 @@
         <v>0</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L73" s="3"/>
       <c r="M73" s="3"/>
@@ -4486,7 +4486,7 @@
         <v>1069</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C74" s="5">
         <v>1</v>
@@ -4495,13 +4495,13 @@
         <v>4</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H74" s="5">
         <v>39</v>
@@ -4510,10 +4510,10 @@
         <v>0</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L74" s="3"/>
       <c r="M74" s="3"/>
@@ -4602,7 +4602,7 @@
         <v>2002</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C78" s="5">
         <v>2</v>
@@ -4610,32 +4610,32 @@
       <c r="D78" s="5">
         <v>4</v>
       </c>
-      <c r="E78" s="5">
-        <v>179329</v>
+      <c r="E78" s="5" t="s">
+        <v>226</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="H78" s="5">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I78" s="5">
-        <v>170</v>
+        <v>39</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N78" s="5">
         <v>194519</v>
@@ -4698,7 +4698,7 @@
         <v>3001</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C81" s="5">
         <v>3</v>
@@ -4710,10 +4710,10 @@
         <v>26755</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H81" s="5">
         <v>5</v>
@@ -4742,7 +4742,7 @@
         <v>3002</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C82" s="5">
         <v>3</v>
@@ -4754,10 +4754,10 @@
         <v>278406</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H82" s="5">
         <v>130</v>
@@ -4766,16 +4766,16 @@
         <v>130</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N82" s="5">
         <v>278406</v>
